--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_25_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_25_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1338,13 +1338,13 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
         <v>7</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2119,16 +2119,16 @@
         <v>11</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
         <v>7</v>
@@ -2321,10 +2321,10 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
         <v>1</v>
@@ -2707,10 +2707,10 @@
         <v>12</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3102,13 +3102,13 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>123</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X30" t="n">
         <v>24</v>
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4883,13 +4883,13 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X38" t="n">
         <v>3</v>
@@ -5076,7 +5076,7 @@
         <v>15</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>10</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6588,16 +6588,16 @@
         <v>70</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X47" t="n">
         <v>15</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_25_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_25_EL.xlsx
@@ -674,10 +674,10 @@
         <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
         <v>12</v>
@@ -833,10 +833,10 @@
         <v>14</v>
       </c>
       <c r="N3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
         <v>11</v>
@@ -1347,14 +1347,14 @@
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1739,14 +1739,14 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -1935,14 +1935,14 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2131,10 +2131,10 @@
         <v>2</v>
       </c>
       <c r="X21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2719,14 +2719,14 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -2915,10 +2915,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3839,10 +3839,10 @@
         <v>5</v>
       </c>
       <c r="X30" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="Y30" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -4892,14 +4892,14 @@
         <v>2</v>
       </c>
       <c r="X38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5088,14 +5088,14 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6600,10 +6600,10 @@
         <v>2</v>
       </c>
       <c r="X47" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
